--- a/artfynd/A 36880-2021 artfynd.xlsx
+++ b/artfynd/A 36880-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127286942</v>
       </c>
       <c r="B2" t="n">
-        <v>97316</v>
+        <v>97322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>127286952</v>
       </c>
       <c r="B3" t="n">
-        <v>97401</v>
+        <v>97407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>127286940</v>
       </c>
       <c r="B4" t="n">
-        <v>97401</v>
+        <v>97407</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36880-2021 artfynd.xlsx
+++ b/artfynd/A 36880-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127286942</v>
       </c>
       <c r="B2" t="n">
-        <v>97322</v>
+        <v>97323</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>127286952</v>
       </c>
       <c r="B3" t="n">
-        <v>97407</v>
+        <v>97408</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>127286940</v>
       </c>
       <c r="B4" t="n">
-        <v>97407</v>
+        <v>97408</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36880-2021 artfynd.xlsx
+++ b/artfynd/A 36880-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127286942</v>
       </c>
       <c r="B2" t="n">
-        <v>97323</v>
+        <v>97327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>127286952</v>
       </c>
       <c r="B3" t="n">
-        <v>97408</v>
+        <v>97412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>127286940</v>
       </c>
       <c r="B4" t="n">
-        <v>97408</v>
+        <v>97412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36880-2021 artfynd.xlsx
+++ b/artfynd/A 36880-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127286942</v>
       </c>
       <c r="B2" t="n">
-        <v>97327</v>
+        <v>97329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>127286952</v>
       </c>
       <c r="B3" t="n">
-        <v>97412</v>
+        <v>97414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>127286940</v>
       </c>
       <c r="B4" t="n">
-        <v>97412</v>
+        <v>97414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36880-2021 artfynd.xlsx
+++ b/artfynd/A 36880-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127286942</v>
       </c>
       <c r="B2" t="n">
-        <v>97329</v>
+        <v>97335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>127286952</v>
       </c>
       <c r="B3" t="n">
-        <v>97414</v>
+        <v>97420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>127286940</v>
       </c>
       <c r="B4" t="n">
-        <v>97414</v>
+        <v>97420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36880-2021 artfynd.xlsx
+++ b/artfynd/A 36880-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127286942</v>
       </c>
       <c r="B2" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>127286952</v>
       </c>
       <c r="B3" t="n">
-        <v>97420</v>
+        <v>97423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>127286940</v>
       </c>
       <c r="B4" t="n">
-        <v>97420</v>
+        <v>97423</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36880-2021 artfynd.xlsx
+++ b/artfynd/A 36880-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127286942</v>
       </c>
       <c r="B2" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>127286952</v>
       </c>
       <c r="B3" t="n">
-        <v>97423</v>
+        <v>97431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>127286940</v>
       </c>
       <c r="B4" t="n">
-        <v>97423</v>
+        <v>97431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36880-2021 artfynd.xlsx
+++ b/artfynd/A 36880-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127286942</v>
       </c>
       <c r="B2" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>127286952</v>
       </c>
       <c r="B3" t="n">
-        <v>97431</v>
+        <v>97432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>127286940</v>
       </c>
       <c r="B4" t="n">
-        <v>97431</v>
+        <v>97432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36880-2021 artfynd.xlsx
+++ b/artfynd/A 36880-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127286942</v>
       </c>
       <c r="B2" t="n">
-        <v>97347</v>
+        <v>97348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>127286952</v>
       </c>
       <c r="B3" t="n">
-        <v>97432</v>
+        <v>97433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>127286940</v>
       </c>
       <c r="B4" t="n">
-        <v>97432</v>
+        <v>97433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36880-2021 artfynd.xlsx
+++ b/artfynd/A 36880-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127286942</v>
       </c>
       <c r="B2" t="n">
-        <v>97348</v>
+        <v>97316</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>127286952</v>
       </c>
       <c r="B3" t="n">
-        <v>97433</v>
+        <v>97401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>127286940</v>
       </c>
       <c r="B4" t="n">
-        <v>97433</v>
+        <v>97401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
